--- a/nr-update-cycle/ig/StructureDefinition-fr-core-encounter.xlsx
+++ b/nr-update-cycle/ig/StructureDefinition-fr-core-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T13:47:13+00:00</t>
+    <t>2026-06-12T13:49:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-cycle/ig/StructureDefinition-fr-core-encounter.xlsx
+++ b/nr-update-cycle/ig/StructureDefinition-fr-core-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T13:49:15+00:00</t>
+    <t>2026-06-12T14:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
